--- a/assessment_forms/034_git_commands_quiz--assessment_forms.xlsx
+++ b/assessment_forms/034_git_commands_quiz--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Which of the following are Git commands?</t>
+          <t>Git Command</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date (2)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time (2)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Note (2)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>First name</t>
+          <t>First Name2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Last name</t>
+          <t>Last Name2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Option 4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
